--- a/Results/Phase 2/Methanol/methanol human toxicity carcinogenic results.xlsx
+++ b/Results/Phase 2/Methanol/methanol human toxicity carcinogenic results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.605417090292047e-10</v>
+        <v>1.478841609333678e-10</v>
       </c>
       <c r="C33" t="n">
-        <v>1.60091077002862e-10</v>
+        <v>1.540664206001771e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>1.545231735077117e-10</v>
+        <v>1.435988193924228e-10</v>
       </c>
       <c r="E33" t="n">
-        <v>1.643903191883918e-10</v>
+        <v>1.591712220136942e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>1.493808367433957e-10</v>
+        <v>1.404917649853646e-10</v>
       </c>
       <c r="G33" t="n">
-        <v>1.62683966618277e-10</v>
+        <v>1.490441764042928e-10</v>
       </c>
       <c r="H33" t="n">
-        <v>1.488729930871601e-10</v>
+        <v>1.401212715304079e-10</v>
       </c>
       <c r="I33" t="n">
-        <v>1.561364931734891e-10</v>
+        <v>1.44471233224873e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>1.584416118769577e-10</v>
+        <v>1.463384363891768e-10</v>
       </c>
       <c r="K33" t="n">
-        <v>1.668217398707622e-10</v>
+        <v>1.50823535385621e-10</v>
       </c>
       <c r="L33" t="n">
-        <v>1.709252759645772e-10</v>
+        <v>1.536642749836817e-10</v>
       </c>
       <c r="M33" t="n">
-        <v>1.807542625050186e-10</v>
+        <v>1.586992224531334e-10</v>
       </c>
       <c r="N33" t="n">
-        <v>1.569528328195829e-10</v>
+        <v>1.451790649285457e-10</v>
       </c>
       <c r="O33" t="n">
-        <v>3.993060734647474e-10</v>
+        <v>3.901346639912306e-10</v>
       </c>
       <c r="P33" t="n">
-        <v>1.539486901327561e-10</v>
+        <v>1.43825687066483e-10</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.471787681748347e-10</v>
+        <v>1.393898011952823e-10</v>
       </c>
       <c r="R33" t="n">
-        <v>1.478023253709111e-10</v>
+        <v>1.395934947673362e-10</v>
       </c>
       <c r="S33" t="n">
-        <v>1.559747338868882e-10</v>
+        <v>1.449451255044811e-10</v>
       </c>
       <c r="T33" t="n">
-        <v>1.522626094402403e-10</v>
+        <v>1.422639380570331e-10</v>
       </c>
       <c r="U33" t="n">
-        <v>4.200309794038004e-10</v>
+        <v>4.007704452681995e-10</v>
       </c>
       <c r="V33" t="n">
-        <v>1.495266675502032e-10</v>
+        <v>1.413208743132682e-10</v>
       </c>
       <c r="W33" t="n">
-        <v>4.308782968127026e-10</v>
+        <v>4.190903311158791e-10</v>
       </c>
       <c r="X33" t="n">
-        <v>1.531429176307143e-10</v>
+        <v>1.428474702239329e-10</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.55279456071909e-10</v>
+        <v>1.4427271864352e-10</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.311059324840569e-10</v>
+        <v>4.209585944377849e-10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.484062345039261e-10</v>
+        <v>1.401998268248668e-10</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.986993277174804e-10</v>
+        <v>1.685964012933876e-10</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.269784887671728e-10</v>
+        <v>1.20734098570517e-10</v>
       </c>
       <c r="C33" t="n">
-        <v>1.40602322312061e-10</v>
+        <v>1.343394639486442e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>1.303063666432937e-10</v>
+        <v>1.224329737126241e-10</v>
       </c>
       <c r="E33" t="n">
-        <v>1.473331659774082e-10</v>
+        <v>1.437481025456796e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>1.290960868554547e-10</v>
+        <v>1.216474106694372e-10</v>
       </c>
       <c r="G33" t="n">
-        <v>1.292318271550049e-10</v>
+        <v>1.221202373637736e-10</v>
       </c>
       <c r="H33" t="n">
-        <v>1.288513706413462e-10</v>
+        <v>1.213707484049595e-10</v>
       </c>
       <c r="I33" t="n">
-        <v>1.307595871863742e-10</v>
+        <v>1.226201870859359e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>1.295121692820103e-10</v>
+        <v>1.221663799238187e-10</v>
       </c>
       <c r="K33" t="n">
-        <v>1.303579464957667e-10</v>
+        <v>1.22578841096563e-10</v>
       </c>
       <c r="L33" t="n">
-        <v>1.292277725710351e-10</v>
+        <v>1.220122241028035e-10</v>
       </c>
       <c r="M33" t="n">
-        <v>1.294083480913143e-10</v>
+        <v>1.218213079857795e-10</v>
       </c>
       <c r="N33" t="n">
-        <v>1.267649251148571e-10</v>
+        <v>1.20368689080886e-10</v>
       </c>
       <c r="O33" t="n">
-        <v>3.228556174147092e-10</v>
+        <v>3.174688512158992e-10</v>
       </c>
       <c r="P33" t="n">
-        <v>1.253503116557711e-10</v>
+        <v>1.19752640513632e-10</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.278241470358902e-10</v>
+        <v>1.21062869998971e-10</v>
       </c>
       <c r="R33" t="n">
-        <v>1.326224870659669e-10</v>
+        <v>1.236273848936715e-10</v>
       </c>
       <c r="S33" t="n">
-        <v>1.282978886992707e-10</v>
+        <v>1.215364902992052e-10</v>
       </c>
       <c r="T33" t="n">
-        <v>1.272478557273643e-10</v>
+        <v>1.205726828634149e-10</v>
       </c>
       <c r="U33" t="n">
-        <v>3.227900670917775e-10</v>
+        <v>3.154263622739883e-10</v>
       </c>
       <c r="V33" t="n">
-        <v>1.284018526131357e-10</v>
+        <v>1.218049034282062e-10</v>
       </c>
       <c r="W33" t="n">
-        <v>3.657426466869618e-10</v>
+        <v>3.507096762624532e-10</v>
       </c>
       <c r="X33" t="n">
-        <v>1.380863036515734e-10</v>
+        <v>1.271737158699977e-10</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.396161537043286e-10</v>
+        <v>1.279918527406297e-10</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.839733882475283e-10</v>
+        <v>3.771666805475509e-10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.303419034508395e-10</v>
+        <v>1.225316655724079e-10</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.336141944701909e-10</v>
+        <v>1.241164294105585e-10</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.525730312118262e-10</v>
+        <v>1.412077044946556e-10</v>
       </c>
       <c r="C33" t="n">
-        <v>1.546420166942869e-10</v>
+        <v>1.485212724928143e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>1.490277417956804e-10</v>
+        <v>1.384335358861045e-10</v>
       </c>
       <c r="E33" t="n">
-        <v>1.602232229184439e-10</v>
+        <v>1.552846625455195e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>1.401695785138731e-10</v>
+        <v>1.332120299162594e-10</v>
       </c>
       <c r="G33" t="n">
-        <v>1.573604608983872e-10</v>
+        <v>1.440069570512955e-10</v>
       </c>
       <c r="H33" t="n">
-        <v>1.398732857243122e-10</v>
+        <v>1.329589062718734e-10</v>
       </c>
       <c r="I33" t="n">
-        <v>1.446429823469659e-10</v>
+        <v>1.35833285213598e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>1.52849345684292e-10</v>
+        <v>1.411001399685394e-10</v>
       </c>
       <c r="K33" t="n">
-        <v>1.571267592819479e-10</v>
+        <v>1.435066198174364e-10</v>
       </c>
       <c r="L33" t="n">
-        <v>1.651395280425477e-10</v>
+        <v>1.483158699736254e-10</v>
       </c>
       <c r="M33" t="n">
-        <v>1.723747916656372e-10</v>
+        <v>1.519085545425212e-10</v>
       </c>
       <c r="N33" t="n">
-        <v>1.43178398669214e-10</v>
+        <v>1.351322538667077e-10</v>
       </c>
       <c r="O33" t="n">
-        <v>3.772255033759287e-10</v>
+        <v>3.693360402336555e-10</v>
       </c>
       <c r="P33" t="n">
-        <v>1.511723647665802e-10</v>
+        <v>1.403019785466462e-10</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.407072722901265e-10</v>
+        <v>1.3365457904905e-10</v>
       </c>
       <c r="R33" t="n">
-        <v>1.404652517562606e-10</v>
+        <v>1.333714711640256e-10</v>
       </c>
       <c r="S33" t="n">
-        <v>1.514599415650623e-10</v>
+        <v>1.403910697459609e-10</v>
       </c>
       <c r="T33" t="n">
-        <v>1.416398916841186e-10</v>
+        <v>1.341236069477716e-10</v>
       </c>
       <c r="U33" t="n">
-        <v>3.955759036489779e-10</v>
+        <v>3.783630814342563e-10</v>
       </c>
       <c r="V33" t="n">
-        <v>1.41479624371555e-10</v>
+        <v>1.346100255414133e-10</v>
       </c>
       <c r="W33" t="n">
-        <v>4.123702448160796e-10</v>
+        <v>3.995924559276461e-10</v>
       </c>
       <c r="X33" t="n">
-        <v>1.50428996239766e-10</v>
+        <v>1.393246992613458e-10</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.496314639234613e-10</v>
+        <v>1.390374634858663e-10</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.173624547401962e-10</v>
+        <v>4.081611764856749e-10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.415957750813959e-10</v>
+        <v>1.342545400244847e-10</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.923009062965719e-10</v>
+        <v>1.629123083884165e-10</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.469765673143539e-10</v>
+        <v>1.366757756390543e-10</v>
       </c>
       <c r="C33" t="n">
-        <v>1.510855983769789e-10</v>
+        <v>1.451118643558276e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>1.499002295443752e-10</v>
+        <v>1.378396613913104e-10</v>
       </c>
       <c r="E33" t="n">
-        <v>1.592557789486157e-10</v>
+        <v>1.538956049826334e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>1.387711473719412e-10</v>
+        <v>1.312865201345567e-10</v>
       </c>
       <c r="G33" t="n">
-        <v>1.53081316497183e-10</v>
+        <v>1.40409144034972e-10</v>
       </c>
       <c r="H33" t="n">
-        <v>1.357983944184013e-10</v>
+        <v>1.294651858919783e-10</v>
       </c>
       <c r="I33" t="n">
-        <v>1.439930115712049e-10</v>
+        <v>1.34323007627773e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>1.492512919853153e-10</v>
+        <v>1.378642170649987e-10</v>
       </c>
       <c r="K33" t="n">
-        <v>1.421488133694882e-10</v>
+        <v>1.335047669740757e-10</v>
       </c>
       <c r="L33" t="n">
-        <v>1.592166154704548e-10</v>
+        <v>1.43720295272862e-10</v>
       </c>
       <c r="M33" t="n">
-        <v>1.660352643302818e-10</v>
+        <v>1.470781230100179e-10</v>
       </c>
       <c r="N33" t="n">
-        <v>1.36081730470909e-10</v>
+        <v>1.298348465252358e-10</v>
       </c>
       <c r="O33" t="n">
-        <v>3.633145891232039e-10</v>
+        <v>3.563008212772385e-10</v>
       </c>
       <c r="P33" t="n">
-        <v>1.477702783677144e-10</v>
+        <v>1.372080620377464e-10</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.400630230152543e-10</v>
+        <v>1.321968594102965e-10</v>
       </c>
       <c r="R33" t="n">
-        <v>1.357873848333297e-10</v>
+        <v>1.295255433598828e-10</v>
       </c>
       <c r="S33" t="n">
-        <v>1.481434801467925e-10</v>
+        <v>1.37343940966843e-10</v>
       </c>
       <c r="T33" t="n">
-        <v>1.372330596511382e-10</v>
+        <v>1.304231034242657e-10</v>
       </c>
       <c r="U33" t="n">
-        <v>3.768863817706043e-10</v>
+        <v>3.624114620952177e-10</v>
       </c>
       <c r="V33" t="n">
-        <v>1.403536243196951e-10</v>
+        <v>1.328942029977444e-10</v>
       </c>
       <c r="W33" t="n">
-        <v>3.997065100613221e-10</v>
+        <v>3.867842555281567e-10</v>
       </c>
       <c r="X33" t="n">
-        <v>1.527462381589217e-10</v>
+        <v>1.395840442444225e-10</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.565085156283769e-10</v>
+        <v>1.420272825131108e-10</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.109585400082345e-10</v>
+        <v>4.019589620883257e-10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.386470443191911e-10</v>
+        <v>1.313999660858268e-10</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.858650862634784e-10</v>
+        <v>1.580252168214625e-10</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.431891893764014e-10</v>
+        <v>1.338078540251883e-10</v>
       </c>
       <c r="C33" t="n">
-        <v>1.48229295006526e-10</v>
+        <v>1.42594111744099e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>1.44695245325339e-10</v>
+        <v>1.342214393464414e-10</v>
       </c>
       <c r="E33" t="n">
-        <v>1.560779375862024e-10</v>
+        <v>1.514943938218644e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>1.383612591690406e-10</v>
+        <v>1.303795058401892e-10</v>
       </c>
       <c r="G33" t="n">
-        <v>1.491804364264497e-10</v>
+        <v>1.375066185512301e-10</v>
       </c>
       <c r="H33" t="n">
-        <v>1.346621970193155e-10</v>
+        <v>1.28108794366785e-10</v>
       </c>
       <c r="I33" t="n">
-        <v>1.407802671385077e-10</v>
+        <v>1.317966554449254e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>1.464340554830746e-10</v>
+        <v>1.355819132274236e-10</v>
       </c>
       <c r="K33" t="n">
-        <v>1.400633904698668e-10</v>
+        <v>1.315935110576971e-10</v>
       </c>
       <c r="L33" t="n">
-        <v>1.533722058479154e-10</v>
+        <v>1.397519189103516e-10</v>
       </c>
       <c r="M33" t="n">
-        <v>1.59633722599096e-10</v>
+        <v>1.429311255165599e-10</v>
       </c>
       <c r="N33" t="n">
-        <v>1.323829167283955e-10</v>
+        <v>1.26977826588551e-10</v>
       </c>
       <c r="O33" t="n">
-        <v>3.550693093186386e-10</v>
+        <v>3.484452585142487e-10</v>
       </c>
       <c r="P33" t="n">
-        <v>1.444819703289537e-10</v>
+        <v>1.34652967540212e-10</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.376974592014647e-10</v>
+        <v>1.301655302297067e-10</v>
       </c>
       <c r="R33" t="n">
-        <v>1.369285523028496e-10</v>
+        <v>1.294841096477552e-10</v>
       </c>
       <c r="S33" t="n">
-        <v>1.458416658950981e-10</v>
+        <v>1.353448956176018e-10</v>
       </c>
       <c r="T33" t="n">
-        <v>1.371304412243785e-10</v>
+        <v>1.296729386921428e-10</v>
       </c>
       <c r="U33" t="n">
-        <v>3.703830993547696e-10</v>
+        <v>3.557956393547228e-10</v>
       </c>
       <c r="V33" t="n">
-        <v>1.426982045016349e-10</v>
+        <v>1.337522412428469e-10</v>
       </c>
       <c r="W33" t="n">
-        <v>3.916966364412904e-10</v>
+        <v>3.787637823560617e-10</v>
       </c>
       <c r="X33" t="n">
-        <v>1.533304826950055e-10</v>
+        <v>1.394065163226527e-10</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.678354590589532e-10</v>
+        <v>1.479442473690041e-10</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.067034775292639e-10</v>
+        <v>3.980356531172344e-10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.376057015745411e-10</v>
+        <v>1.301064529265334e-10</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.803119981209182e-10</v>
+        <v>1.543130266473265e-10</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.275348724859208e-10</v>
+        <v>1.209812710758819e-10</v>
       </c>
       <c r="C33" t="n">
-        <v>1.376208535831764e-10</v>
+        <v>1.32336569610754e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>1.35268970891313e-10</v>
+        <v>1.251858355440782e-10</v>
       </c>
       <c r="E33" t="n">
-        <v>1.477377304793533e-10</v>
+        <v>1.439369243597955e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>1.269890802773548e-10</v>
+        <v>1.202891698227019e-10</v>
       </c>
       <c r="G33" t="n">
-        <v>1.299558767282893e-10</v>
+        <v>1.224984552056063e-10</v>
       </c>
       <c r="H33" t="n">
-        <v>1.304114169926642e-10</v>
+        <v>1.22153561687952e-10</v>
       </c>
       <c r="I33" t="n">
-        <v>1.28687931016296e-10</v>
+        <v>1.212884719748726e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>1.301043533047868e-10</v>
+        <v>1.224975575376133e-10</v>
       </c>
       <c r="K33" t="n">
-        <v>1.368697690202205e-10</v>
+        <v>1.26399305706841e-10</v>
       </c>
       <c r="L33" t="n">
-        <v>1.34670088772203e-10</v>
+        <v>1.253370166995262e-10</v>
       </c>
       <c r="M33" t="n">
-        <v>1.376932243561047e-10</v>
+        <v>1.267739800698687e-10</v>
       </c>
       <c r="N33" t="n">
-        <v>1.325782676109412e-10</v>
+        <v>1.237788178803753e-10</v>
       </c>
       <c r="O33" t="n">
-        <v>3.243796527662165e-10</v>
+        <v>3.186391684206385e-10</v>
       </c>
       <c r="P33" t="n">
-        <v>1.286199979709084e-10</v>
+        <v>1.216482234023941e-10</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.291008972016509e-10</v>
+        <v>1.217069578696422e-10</v>
       </c>
       <c r="R33" t="n">
-        <v>1.282876737934969e-10</v>
+        <v>1.210043314815363e-10</v>
       </c>
       <c r="S33" t="n">
-        <v>1.294643114316928e-10</v>
+        <v>1.222813686551062e-10</v>
       </c>
       <c r="T33" t="n">
-        <v>1.272062195242189e-10</v>
+        <v>1.204661092255607e-10</v>
       </c>
       <c r="U33" t="n">
-        <v>3.276083234483947e-10</v>
+        <v>3.179970921862667e-10</v>
       </c>
       <c r="V33" t="n">
-        <v>1.259696976395859e-10</v>
+        <v>1.202058792127656e-10</v>
       </c>
       <c r="W33" t="n">
-        <v>3.531258786296134e-10</v>
+        <v>3.427693292989912e-10</v>
       </c>
       <c r="X33" t="n">
-        <v>1.298798799128464e-10</v>
+        <v>1.220704654139666e-10</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.273614670107933e-10</v>
+        <v>1.206685260992948e-10</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.843804033645615e-10</v>
+        <v>3.77256046493606e-10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.269378865678101e-10</v>
+        <v>1.204247036111478e-10</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.398896579794072e-10</v>
+        <v>1.277000199701972e-10</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.246204617620152e-10</v>
+        <v>1.175027725210042e-10</v>
       </c>
       <c r="C33" t="n">
-        <v>1.347743881114829e-10</v>
+        <v>1.285920478088027e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>1.275708778090819e-10</v>
+        <v>1.189805110773603e-10</v>
       </c>
       <c r="E33" t="n">
-        <v>1.433389261272948e-10</v>
+        <v>1.39995077108203e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>1.253299302509351e-10</v>
+        <v>1.175709914266401e-10</v>
       </c>
       <c r="G33" t="n">
-        <v>1.224433690456093e-10</v>
+        <v>1.161775570489583e-10</v>
       </c>
       <c r="H33" t="n">
-        <v>1.248751439600526e-10</v>
+        <v>1.171393847793412e-10</v>
       </c>
       <c r="I33" t="n">
-        <v>1.261042654375025e-10</v>
+        <v>1.180083733190171e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>1.237243217575724e-10</v>
+        <v>1.169055428755546e-10</v>
       </c>
       <c r="K33" t="n">
-        <v>1.248015848366764e-10</v>
+        <v>1.173896305402087e-10</v>
       </c>
       <c r="L33" t="n">
-        <v>1.250983862344927e-10</v>
+        <v>1.178409088266108e-10</v>
       </c>
       <c r="M33" t="n">
-        <v>1.247130437985497e-10</v>
+        <v>1.172779193806493e-10</v>
       </c>
       <c r="N33" t="n">
-        <v>1.231373471293659e-10</v>
+        <v>1.164234897459496e-10</v>
       </c>
       <c r="O33" t="n">
-        <v>3.069439470226572e-10</v>
+        <v>3.011131708416494e-10</v>
       </c>
       <c r="P33" t="n">
-        <v>1.202749745670169e-10</v>
+        <v>1.148633369386694e-10</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.222876744261948e-10</v>
+        <v>1.159767950751085e-10</v>
       </c>
       <c r="R33" t="n">
-        <v>1.261701556886806e-10</v>
+        <v>1.179838162283374e-10</v>
       </c>
       <c r="S33" t="n">
-        <v>1.240257432317746e-10</v>
+        <v>1.172346646345305e-10</v>
       </c>
       <c r="T33" t="n">
-        <v>1.227087208912154e-10</v>
+        <v>1.160482263078243e-10</v>
       </c>
       <c r="U33" t="n">
-        <v>3.003269488946733e-10</v>
+        <v>2.940474361925435e-10</v>
       </c>
       <c r="V33" t="n">
-        <v>1.225253904702034e-10</v>
+        <v>1.164380190854588e-10</v>
       </c>
       <c r="W33" t="n">
-        <v>3.327866118234871e-10</v>
+        <v>3.225195193940605e-10</v>
       </c>
       <c r="X33" t="n">
-        <v>1.316475823500425e-10</v>
+        <v>1.21508858088642e-10</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.273680758117901e-10</v>
+        <v>1.189044948728112e-10</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.735788657990473e-10</v>
+        <v>3.667251957564005e-10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.244398737723834e-10</v>
+        <v>1.171795766124556e-10</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.258540108122243e-10</v>
+        <v>1.178067141638479e-10</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.264732305203598e-10</v>
+        <v>1.185170426563208e-10</v>
       </c>
       <c r="C33" t="n">
-        <v>1.351471966721259e-10</v>
+        <v>1.286500500369098e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>1.276687184658726e-10</v>
+        <v>1.188595852792381e-10</v>
       </c>
       <c r="E33" t="n">
-        <v>1.453689562226741e-10</v>
+        <v>1.411473265942915e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>1.239836772589618e-10</v>
+        <v>1.1658762228794e-10</v>
       </c>
       <c r="G33" t="n">
-        <v>1.250202050886201e-10</v>
+        <v>1.176417364530333e-10</v>
       </c>
       <c r="H33" t="n">
-        <v>1.239124330133034e-10</v>
+        <v>1.164397260395923e-10</v>
       </c>
       <c r="I33" t="n">
-        <v>1.256633598249594e-10</v>
+        <v>1.175863758762223e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>1.247816510606164e-10</v>
+        <v>1.17369571307612e-10</v>
       </c>
       <c r="K33" t="n">
-        <v>1.238472701277571e-10</v>
+        <v>1.166327665765876e-10</v>
       </c>
       <c r="L33" t="n">
-        <v>1.23986505438163e-10</v>
+        <v>1.169398117245873e-10</v>
       </c>
       <c r="M33" t="n">
-        <v>1.235379807879693e-10</v>
+        <v>1.163493705985629e-10</v>
       </c>
       <c r="N33" t="n">
-        <v>1.226795082014326e-10</v>
+        <v>1.159757521694474e-10</v>
       </c>
       <c r="O33" t="n">
-        <v>3.042966834966468e-10</v>
+        <v>2.984497250413967e-10</v>
       </c>
       <c r="P33" t="n">
-        <v>1.205050359609301e-10</v>
+        <v>1.148740201707223e-10</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.218293276244289e-10</v>
+        <v>1.154962101121251e-10</v>
       </c>
       <c r="R33" t="n">
-        <v>1.273851107721429e-10</v>
+        <v>1.185241258120724e-10</v>
       </c>
       <c r="S33" t="n">
-        <v>1.233425093481755e-10</v>
+        <v>1.165965377491595e-10</v>
       </c>
       <c r="T33" t="n">
-        <v>1.226007962995069e-10</v>
+        <v>1.158222359328849e-10</v>
       </c>
       <c r="U33" t="n">
-        <v>2.992046780895843e-10</v>
+        <v>2.926056217053322e-10</v>
       </c>
       <c r="V33" t="n">
-        <v>1.231277107713718e-10</v>
+        <v>1.166631255318015e-10</v>
       </c>
       <c r="W33" t="n">
-        <v>3.472582319047715e-10</v>
+        <v>3.304779889045944e-10</v>
       </c>
       <c r="X33" t="n">
-        <v>1.331114813751243e-10</v>
+        <v>1.223025055400958e-10</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.287278010445239e-10</v>
+        <v>1.195398283255874e-10</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.714632235657024e-10</v>
+        <v>3.648370920264882e-10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.244657765584672e-10</v>
+        <v>1.170453236629999e-10</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.278068710036496e-10</v>
+        <v>1.187147965936068e-10</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.383643255871835e-10</v>
+        <v>1.295593466600754e-10</v>
       </c>
       <c r="C33" t="n">
-        <v>1.44327640348745e-10</v>
+        <v>1.385653832152539e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>1.387272303815581e-10</v>
+        <v>1.292510680222211e-10</v>
       </c>
       <c r="E33" t="n">
-        <v>1.531447437566638e-10</v>
+        <v>1.487404494260149e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>1.334699057617265e-10</v>
+        <v>1.261431089339327e-10</v>
       </c>
       <c r="G33" t="n">
-        <v>1.48153886729262e-10</v>
+        <v>1.356004851540795e-10</v>
       </c>
       <c r="H33" t="n">
-        <v>1.325735650711686e-10</v>
+        <v>1.255210270571336e-10</v>
       </c>
       <c r="I33" t="n">
-        <v>1.386193169000023e-10</v>
+        <v>1.29157758218571e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>1.43231832886755e-10</v>
+        <v>1.324117615415653e-10</v>
       </c>
       <c r="K33" t="n">
-        <v>1.458994231148431e-10</v>
+        <v>1.338541177989139e-10</v>
       </c>
       <c r="L33" t="n">
-        <v>1.542554954137398e-10</v>
+        <v>1.389538540455137e-10</v>
       </c>
       <c r="M33" t="n">
-        <v>1.628752923815529e-10</v>
+        <v>1.438133948724515e-10</v>
       </c>
       <c r="N33" t="n">
-        <v>1.410101755721582e-10</v>
+        <v>1.307253842440798e-10</v>
       </c>
       <c r="O33" t="n">
-        <v>3.450620625109937e-10</v>
+        <v>3.380574291767826e-10</v>
       </c>
       <c r="P33" t="n">
-        <v>1.403295157231258e-10</v>
+        <v>1.307226193597425e-10</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.340557420252179e-10</v>
+        <v>1.266400388787932e-10</v>
       </c>
       <c r="R33" t="n">
-        <v>1.339298416215714e-10</v>
+        <v>1.263739921774533e-10</v>
       </c>
       <c r="S33" t="n">
-        <v>1.383141911861167e-10</v>
+        <v>1.295668098020236e-10</v>
       </c>
       <c r="T33" t="n">
-        <v>1.354231860413716e-10</v>
+        <v>1.273200298912961e-10</v>
       </c>
       <c r="U33" t="n">
-        <v>3.573398625911814e-10</v>
+        <v>3.427232344501072e-10</v>
       </c>
       <c r="V33" t="n">
-        <v>1.324454072393129e-10</v>
+        <v>1.261126637479438e-10</v>
       </c>
       <c r="W33" t="n">
-        <v>3.714220996908023e-10</v>
+        <v>3.611756396819137e-10</v>
       </c>
       <c r="X33" t="n">
-        <v>1.449465986153006e-10</v>
+        <v>1.329602463471651e-10</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.403492877371431e-10</v>
+        <v>1.304330104921444e-10</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.980916249774576e-10</v>
+        <v>3.895556503683143e-10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.327417669638e-10</v>
+        <v>1.259008127063044e-10</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.766963358543108e-10</v>
+        <v>1.507687737634394e-10</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.287055794915537e-10</v>
+        <v>1.22403020483197e-10</v>
       </c>
       <c r="C33" t="n">
-        <v>1.429826080322933e-10</v>
+        <v>1.365066200210718e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>1.324544790848384e-10</v>
+        <v>1.243289271617266e-10</v>
       </c>
       <c r="E33" t="n">
-        <v>1.492542840905046e-10</v>
+        <v>1.454375100993089e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>1.303487643478278e-10</v>
+        <v>1.230477384853467e-10</v>
       </c>
       <c r="G33" t="n">
-        <v>1.402203081374032e-10</v>
+        <v>1.296257984825985e-10</v>
       </c>
       <c r="H33" t="n">
-        <v>1.286195040505212e-10</v>
+        <v>1.219106349844504e-10</v>
       </c>
       <c r="I33" t="n">
-        <v>1.32010622316025e-10</v>
+        <v>1.239942595387226e-10</v>
       </c>
       <c r="J33" t="n">
-        <v>1.340177878952483e-10</v>
+        <v>1.25618372153351e-10</v>
       </c>
       <c r="K33" t="n">
-        <v>1.339052697193155e-10</v>
+        <v>1.253729202415775e-10</v>
       </c>
       <c r="L33" t="n">
-        <v>1.373281932221108e-10</v>
+        <v>1.276345885704643e-10</v>
       </c>
       <c r="M33" t="n">
-        <v>1.345685280167911e-10</v>
+        <v>1.256184492471357e-10</v>
       </c>
       <c r="N33" t="n">
-        <v>1.281409895132322e-10</v>
+        <v>1.218473907008732e-10</v>
       </c>
       <c r="O33" t="n">
-        <v>3.291987285764907e-10</v>
+        <v>3.237384018310871e-10</v>
       </c>
       <c r="P33" t="n">
-        <v>1.321725066156066e-10</v>
+        <v>1.245623749990283e-10</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.316491031554206e-10</v>
+        <v>1.240626141819041e-10</v>
       </c>
       <c r="R33" t="n">
-        <v>1.319007700865007e-10</v>
+        <v>1.238771179642533e-10</v>
       </c>
       <c r="S33" t="n">
-        <v>1.307807788878654e-10</v>
+        <v>1.237098004198865e-10</v>
       </c>
       <c r="T33" t="n">
-        <v>1.290702775219588e-10</v>
+        <v>1.223113694206245e-10</v>
       </c>
       <c r="U33" t="n">
-        <v>3.279457642692691e-10</v>
+        <v>3.205604897393352e-10</v>
       </c>
       <c r="V33" t="n">
-        <v>1.285214387585342e-10</v>
+        <v>1.224917355611876e-10</v>
       </c>
       <c r="W33" t="n">
-        <v>3.592586617915035e-10</v>
+        <v>3.490367336243421e-10</v>
       </c>
       <c r="X33" t="n">
-        <v>1.391603918481744e-10</v>
+        <v>1.28375166189231e-10</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.450846293822261e-10</v>
+        <v>1.319826901827617e-10</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.863068601069834e-10</v>
+        <v>3.796647630767607e-10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.297586514929053e-10</v>
+        <v>1.228512856419602e-10</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.578889958539786e-10</v>
+        <v>1.388366195634391e-10</v>
       </c>
     </row>
   </sheetData>
